--- a/dictionary_check_caroline.xlsx
+++ b/dictionary_check_caroline.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t xml:space="preserve">medication</t>
   </si>
@@ -488,19 +488,25 @@
     <t xml:space="preserve">abx_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">other_abx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oral_other_abx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">other_mtz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oral_mtz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vaginal_mtz</t>
+    <t xml:space="preserve">comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm_other_abx</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">cm_oral_mtz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is it ok to categorize metronidazole with missing route as oral metronidazole (cm_oral_mtz) ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is it ok to categorize intramuscular metronidazole as oral metronidazole (cm_oral_mtz) ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cm_vag_mtz</t>
   </si>
 </sst>
 </file>
@@ -2136,6 +2142,9 @@
       <c r="C1" t="s">
         <v>156</v>
       </c>
+      <c r="D1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -2145,7 +2154,10 @@
         <v>132</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="D2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -2158,6 +2170,9 @@
       <c r="C3" t="s">
         <v>158</v>
       </c>
+      <c r="D3" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -2169,6 +2184,9 @@
       <c r="C4" t="s">
         <v>158</v>
       </c>
+      <c r="D4" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -2180,6 +2198,9 @@
       <c r="C5" t="s">
         <v>158</v>
       </c>
+      <c r="D5" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -2189,7 +2210,10 @@
         <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="D6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -2200,7 +2224,10 @@
         <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="D7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="8">
@@ -2213,6 +2240,9 @@
       <c r="C8" t="s">
         <v>160</v>
       </c>
+      <c r="D8" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -2222,7 +2252,10 @@
         <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -2235,6 +2268,9 @@
       <c r="C10" t="s">
         <v>158</v>
       </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -2244,7 +2280,10 @@
         <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="D11" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -2256,6 +2295,9 @@
       </c>
       <c r="C12" t="s">
         <v>158</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/dictionary_check_caroline.xlsx
+++ b/dictionary_check_caroline.xlsx
@@ -1,520 +1,527 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurasymul/Documents/Work/Academia/Research/Projects/01. VIBRANT/VIBRANT-00-QC-and-preprocessing/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A205FE-9802-454A-8317-D6D327AF5770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="medication_is_abx" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="route_description" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="abx_medication_compound" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="abx_compound_route_cat" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="medication_is_abx" sheetId="1" r:id="rId1"/>
+    <sheet name="route_description" sheetId="2" r:id="rId2"/>
+    <sheet name="abx_medication_compound" sheetId="3" r:id="rId3"/>
+    <sheet name="abx_compound_route_cat" sheetId="4" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
-  <si>
-    <t xml:space="preserve">medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_abx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZITHROMYCIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLAGYL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CEFTRIAXONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE 500MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIPROFLOXACIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URIZONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMOXICILLIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUGMENTIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE 500MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENZATHINE BENZYL PENICILLIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENZATHINE BENZYLPENICILLIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOSFOMYCIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACROBID(NITROFURANTOIN) 100MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE (FLAGYL) 500MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE (METROGEL) 0.75 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE 10MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METRONIDAZOLE 500 MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NITROFURANTOIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPO PROVERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUR-ISTERATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETOGEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NURISTERATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLOTRIMAZOLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIPHASIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRUFEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLERGEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARACETAMOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLUCONAZOLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OVRAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORDETTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CETIRIZINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOPERAMIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLUCONAZOLE 150 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDROCORTISONE CREAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONISTAT CREAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYCLOVIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALBUTEROL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALBUTEROL INHALER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALERGEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALESSE (LEVONORGESTREL-ETHNIC ESTRADIOL 01-0.02 MG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLERGEX EYE DROPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZELAIC ACID 15% GEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENADRYL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BENZYL BENZOATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BETAMETHASONE 0.05% LOTION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUPROPION (WELLBUTTEN SR) 150 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUSCOPAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUSPIRONE 5MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHLORHEXIDINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CITALOPRAM 30 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLOBETASOL OINTMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLOTRIMAZOLE CREAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYCLOBENZAPRINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPOT MEDROXYPROGESTERONE ACETATE (DEPO PROVERA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIFLUCAN 150MG (FLUCONAZOLE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXPERT BRAIN BOOSTER MULTIVITAMIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F/TDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEMDOPHILUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLUCONAZOLE 150 MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLUCONAZOLE 150MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLUCONAZOLE 200MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRANDPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HISTACON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDROCORTISONE 1% CREAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDROCORTISONE 2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDROCORTISONE 25MG SUPPOSITORY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDROCORTISONE CREAM 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYPOSPASMOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBUPROFEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBUPROFEN 600 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INSULIN LISPRO (ADMELOG;LUMPROG) 100UNIT/ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRON DEXTRAN 1000MG INFUSION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVERMECTIM 1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNEL FE 1/20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KETOROLAC 9TORADOL) 15MG INJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMOTRIGINE 150 MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANTUS SALOSTAR U-100 INSULIN 100 UNIT/ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONOGESTREL-ETHINYL ESTRADIOL 0.15 - 0.03 MG/TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONOGESTREL-ETHINYL ESTRADIOL 0.15-0.03 MG PER TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTEREL-ETHINYL ESTRADIOL 0.15 - 0.03 MG/TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL- ETHINYL ESTRADIOL 0.1 - 0.02 MG PER TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL- ETHINYL ESTRADIOL 0.1-0.02MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL- ETHINYL ESTRADIOL 0.15-0.03 MG/TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL-ETHINYL ESTRADIOL 0.1-0.02 MG TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL-ETHINYL ESTRADIOL 0.15-0.03MG/TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL-ETHINYL ESTRADIOL TABLET 0.1-0.02 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTREL-ETHINYL ESTRADIOL. 01-0.02 MG PER TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEVONORGESTROL- ETHANYL/ESTRADIOL 0.1-0.02 MG/TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEXAPRO 5MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIDOCAINE CREAM 5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LISDEXAMFETHANE 40MG CAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOPIRAMIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LORAZEPAM 0.5MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDLEMON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METFORMIN ( GLUCOPHAGE) 100 MG TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METHYLPHENIDATE HCI (RITALIN) 5MG TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONOSTAT 7 DAY SUPPOSITORIES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYPROCAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NURISTERATE 0.2 G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NURITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUVARING (ETONOGESTREL-ETHINYL ESTRADIOL) 0.12- 0.015MG/24HR VAGINAL RING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHENAZOPYRIDINE (PYRIDIUM) 100MG TABLET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHENTERMINE 15MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROBIOTICS - ORAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROZAC (FLUOXETINE) 40MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIZATRIPTAN 10 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENIUM SULPHATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELENIUM SULPHIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SODIUM CHLORIDE 0.9% BOLUS 0.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPIRONOLACTONG 50MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNALEVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TACROLIMUS 0.1% OINTMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORADOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAZODONE 50 MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRETINOIN 0.025 % CREAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIAMCINOLONE 0.5% OINTMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYLENOL 500MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULSANIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNKNOWN ANALGESIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALACYCLOVIR 500MG TAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALTREX (VALACYCLOVIR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VENTOLIN INHALER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WEGOVY 2.4 MG/0.75ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOFRAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">route_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intramuscular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaginal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Topical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inhalation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intravenous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subcutaneous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rectal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abx_compound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cephalosporins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluoroquinolones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fosfomycin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macrolides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metronidazole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nitrofurans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penicillins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abx_cat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm_other_abx</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">cm_oral_mtz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is it ok to categorize metronidazole with missing route as oral metronidazole (cm_oral_mtz) ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is it ok to categorize intramuscular metronidazole as oral metronidazole (cm_oral_mtz) ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cm_vag_mtz</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="164">
+  <si>
+    <t>medication</t>
+  </si>
+  <si>
+    <t>is_abx</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE</t>
+  </si>
+  <si>
+    <t>AZITHROMYCIN</t>
+  </si>
+  <si>
+    <t>FLAGYL</t>
+  </si>
+  <si>
+    <t>CEFTRIAXONE</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE 500MG</t>
+  </si>
+  <si>
+    <t>CIPROFLOXACIN</t>
+  </si>
+  <si>
+    <t>URIZONE</t>
+  </si>
+  <si>
+    <t>AMOXICILLIN</t>
+  </si>
+  <si>
+    <t>AUGMENTIN</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE 500MG TAB</t>
+  </si>
+  <si>
+    <t>BENZATHINE BENZYL PENICILLIN</t>
+  </si>
+  <si>
+    <t>BENZATHINE BENZYLPENICILLIN</t>
+  </si>
+  <si>
+    <t>FOSFOMYCIN</t>
+  </si>
+  <si>
+    <t>MACROBID(NITROFURANTOIN) 100MG</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE (FLAGYL) 500MG</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE (METROGEL) 0.75 %</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE 10MG</t>
+  </si>
+  <si>
+    <t>METRONIDAZOLE 500 MG TAB</t>
+  </si>
+  <si>
+    <t>NITROFURANTOIN</t>
+  </si>
+  <si>
+    <t>DEPO PROVERA</t>
+  </si>
+  <si>
+    <t>NUR-ISTERATE</t>
+  </si>
+  <si>
+    <t>PETOGEN</t>
+  </si>
+  <si>
+    <t>NURISTERATE</t>
+  </si>
+  <si>
+    <t>CLOTRIMAZOLE</t>
+  </si>
+  <si>
+    <t>TRIPHASIL</t>
+  </si>
+  <si>
+    <t>BRUFEN</t>
+  </si>
+  <si>
+    <t>ALLERGEX</t>
+  </si>
+  <si>
+    <t>PARACETAMOL</t>
+  </si>
+  <si>
+    <t>FLUCONAZOLE</t>
+  </si>
+  <si>
+    <t>OVRAL</t>
+  </si>
+  <si>
+    <t>PANADO</t>
+  </si>
+  <si>
+    <t>NORDETTE</t>
+  </si>
+  <si>
+    <t>CETIRIZINE</t>
+  </si>
+  <si>
+    <t>LOPERAMIDE</t>
+  </si>
+  <si>
+    <t>FLUCONAZOLE 150 MG</t>
+  </si>
+  <si>
+    <t>HYDROCORTISONE CREAM</t>
+  </si>
+  <si>
+    <t>MONISTAT CREAM</t>
+  </si>
+  <si>
+    <t>ACYCLOVIR</t>
+  </si>
+  <si>
+    <t>ALBUTEROL</t>
+  </si>
+  <si>
+    <t>ALBUTEROL INHALER</t>
+  </si>
+  <si>
+    <t>ALERGEX</t>
+  </si>
+  <si>
+    <t>ALESSE (LEVONORGESTREL-ETHNIC ESTRADIOL 01-0.02 MG)</t>
+  </si>
+  <si>
+    <t>ALLERGEX EYE DROPS</t>
+  </si>
+  <si>
+    <t>AZELAIC ACID 15% GEL</t>
+  </si>
+  <si>
+    <t>BENADRYL</t>
+  </si>
+  <si>
+    <t>BENZYL BENZOATE</t>
+  </si>
+  <si>
+    <t>BETAMETHASONE 0.05% LOTION</t>
+  </si>
+  <si>
+    <t>BUPROPION (WELLBUTTEN SR) 150 MG</t>
+  </si>
+  <si>
+    <t>BUSCOPAN</t>
+  </si>
+  <si>
+    <t>BUSPIRONE 5MG TAB</t>
+  </si>
+  <si>
+    <t>CHLORHEXIDINE</t>
+  </si>
+  <si>
+    <t>CITALOPRAM 30 MG</t>
+  </si>
+  <si>
+    <t>CLOBETASOL OINTMENT</t>
+  </si>
+  <si>
+    <t>CLOTRIMAZOLE CREAM</t>
+  </si>
+  <si>
+    <t>CYCLOBENZAPRINE</t>
+  </si>
+  <si>
+    <t>DEPOT MEDROXYPROGESTERONE ACETATE (DEPO PROVERA)</t>
+  </si>
+  <si>
+    <t>DIFLUCAN 150MG (FLUCONAZOLE)</t>
+  </si>
+  <si>
+    <t>EXPERT BRAIN BOOSTER MULTIVITAMIN</t>
+  </si>
+  <si>
+    <t>F/TDF</t>
+  </si>
+  <si>
+    <t>FEMDOPHILUS</t>
+  </si>
+  <si>
+    <t>FLUCONAZOLE 150 MG TAB</t>
+  </si>
+  <si>
+    <t>FLUCONAZOLE 150MG TAB</t>
+  </si>
+  <si>
+    <t>FLUCONAZOLE 200MG</t>
+  </si>
+  <si>
+    <t>GRANDPA</t>
+  </si>
+  <si>
+    <t>HISTACON</t>
+  </si>
+  <si>
+    <t>HYDROCORTISONE 1% CREAM</t>
+  </si>
+  <si>
+    <t>HYDROCORTISONE 2%</t>
+  </si>
+  <si>
+    <t>HYDROCORTISONE 25MG SUPPOSITORY</t>
+  </si>
+  <si>
+    <t>HYDROCORTISONE CREAM 1%</t>
+  </si>
+  <si>
+    <t>HYPOSPASMOL</t>
+  </si>
+  <si>
+    <t>IBUPROFEN</t>
+  </si>
+  <si>
+    <t>IBUPROFEN 600 MG</t>
+  </si>
+  <si>
+    <t>INSULIN LISPRO (ADMELOG;LUMPROG) 100UNIT/ML</t>
+  </si>
+  <si>
+    <t>IRON DEXTRAN 1000MG INFUSION</t>
+  </si>
+  <si>
+    <t>IVERMECTIM 1%</t>
+  </si>
+  <si>
+    <t>JUNEL FE 1/20</t>
+  </si>
+  <si>
+    <t>KETOROLAC 9TORADOL) 15MG INJ</t>
+  </si>
+  <si>
+    <t>LAMOTRIGINE 150 MG TAB</t>
+  </si>
+  <si>
+    <t>LANTUS SALOSTAR U-100 INSULIN 100 UNIT/ML</t>
+  </si>
+  <si>
+    <t>LEVONOGESTREL-ETHINYL ESTRADIOL 0.15 - 0.03 MG/TAB</t>
+  </si>
+  <si>
+    <t>LEVONOGESTREL-ETHINYL ESTRADIOL 0.15-0.03 MG PER TAB</t>
+  </si>
+  <si>
+    <t>LEVONORGESTEREL-ETHINYL ESTRADIOL 0.15 - 0.03 MG/TAB</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL- ETHINYL ESTRADIOL 0.1 - 0.02 MG PER TAB</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL- ETHINYL ESTRADIOL 0.1-0.02MG</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL- ETHINYL ESTRADIOL 0.15-0.03 MG/TABLET</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL-ETHINYL ESTRADIOL 0.1-0.02 MG TABLET</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL-ETHINYL ESTRADIOL 0.15-0.03MG/TAB</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL-ETHINYL ESTRADIOL TABLET 0.1-0.02 MG</t>
+  </si>
+  <si>
+    <t>LEVONORGESTREL-ETHINYL ESTRADIOL. 01-0.02 MG PER TABLET</t>
+  </si>
+  <si>
+    <t>LEVONORGESTROL- ETHANYL/ESTRADIOL 0.1-0.02 MG/TAB</t>
+  </si>
+  <si>
+    <t>LEXAPRO 5MG</t>
+  </si>
+  <si>
+    <t>LIDOCAINE CREAM 5%</t>
+  </si>
+  <si>
+    <t>LISDEXAMFETHANE 40MG CAP</t>
+  </si>
+  <si>
+    <t>LOPIRAMIDE</t>
+  </si>
+  <si>
+    <t>LORAZEPAM 0.5MG</t>
+  </si>
+  <si>
+    <t>MEDLEMON</t>
+  </si>
+  <si>
+    <t>METFORMIN ( GLUCOPHAGE) 100 MG TABLET</t>
+  </si>
+  <si>
+    <t>METHYLPHENIDATE HCI (RITALIN) 5MG TABLET</t>
+  </si>
+  <si>
+    <t>MONOSTAT 7 DAY SUPPOSITORIES</t>
+  </si>
+  <si>
+    <t>MYPROCAM</t>
+  </si>
+  <si>
+    <t>NURISTERATE 0.2 G</t>
+  </si>
+  <si>
+    <t>NURITA</t>
+  </si>
+  <si>
+    <t>NUVARING (ETONOGESTREL-ETHINYL ESTRADIOL) 0.12- 0.015MG/24HR VAGINAL RING</t>
+  </si>
+  <si>
+    <t>PHENAZOPYRIDINE (PYRIDIUM) 100MG TABLET</t>
+  </si>
+  <si>
+    <t>PHENTERMINE 15MG</t>
+  </si>
+  <si>
+    <t>PROBIOTICS - ORAL</t>
+  </si>
+  <si>
+    <t>PROZAC (FLUOXETINE) 40MG</t>
+  </si>
+  <si>
+    <t>RIZATRIPTAN 10 MG</t>
+  </si>
+  <si>
+    <t>SELENIUM SULPHATE</t>
+  </si>
+  <si>
+    <t>SELENIUM SULPHIDE</t>
+  </si>
+  <si>
+    <t>SODIUM CHLORIDE 0.9% BOLUS 0.9%</t>
+  </si>
+  <si>
+    <t>SPIRONOLACTONG 50MG TAB</t>
+  </si>
+  <si>
+    <t>SYNALEVE</t>
+  </si>
+  <si>
+    <t>TACROLIMUS 0.1% OINTMENT</t>
+  </si>
+  <si>
+    <t>TLD</t>
+  </si>
+  <si>
+    <t>TORADOL</t>
+  </si>
+  <si>
+    <t>TRAZODONE 50 MG</t>
+  </si>
+  <si>
+    <t>TRETINOIN 0.025 % CREAM</t>
+  </si>
+  <si>
+    <t>TRIAMCINOLONE 0.5% OINTMENT</t>
+  </si>
+  <si>
+    <t>TYLENOL 500MG TAB</t>
+  </si>
+  <si>
+    <t>ULSANIC</t>
+  </si>
+  <si>
+    <t>UNKNOWN ANALGESIA</t>
+  </si>
+  <si>
+    <t>VALACYCLOVIR 500MG TAB</t>
+  </si>
+  <si>
+    <t>VALTREX (VALACYCLOVIR)</t>
+  </si>
+  <si>
+    <t>VENTOLIN INHALER</t>
+  </si>
+  <si>
+    <t>WEGOVY 2.4 MG/0.75ML</t>
+  </si>
+  <si>
+    <t>ZOFRAN</t>
+  </si>
+  <si>
+    <t>route</t>
+  </si>
+  <si>
+    <t>route_description</t>
+  </si>
+  <si>
+    <t>IM</t>
+  </si>
+  <si>
+    <t>Intramuscular</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>Oral</t>
+  </si>
+  <si>
+    <t>VAG</t>
+  </si>
+  <si>
+    <t>Vaginal</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>Topical</t>
+  </si>
+  <si>
+    <t>IHL</t>
+  </si>
+  <si>
+    <t>Inhalation</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Intravenous</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>Subcutaneous</t>
+  </si>
+  <si>
+    <t>Blank</t>
+  </si>
+  <si>
+    <t>REC</t>
+  </si>
+  <si>
+    <t>Rectal</t>
+  </si>
+  <si>
+    <t>abx_compound</t>
+  </si>
+  <si>
+    <t>Cephalosporins</t>
+  </si>
+  <si>
+    <t>Fluoroquinolones</t>
+  </si>
+  <si>
+    <t>Fosfomycin</t>
+  </si>
+  <si>
+    <t>Macrolides</t>
+  </si>
+  <si>
+    <t>Metronidazole</t>
+  </si>
+  <si>
+    <t>Nitrofurans</t>
+  </si>
+  <si>
+    <t>Penicillins</t>
+  </si>
+  <si>
+    <t>abx_cat</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>cm_other_abx</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>cm_oral_mtz</t>
+  </si>
+  <si>
+    <t>cm_vag_mtz</t>
+  </si>
+  <si>
+    <t>There was one participant with one "Metronidazole" but no route specified. Is it ok to assume it was oral metronidazole (cm_oral_mtz) ?</t>
+  </si>
+  <si>
+    <t>There was one participant with one "Metronidazole" CM and "intramuscular" as the route. From what we've looked at, it is not impossible, but quite unlikely.  Is it ok to assume it was oral metronidazole (cm_oral_mtz) ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -523,12 +530,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -543,13 +568,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -831,11 +868,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B128"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -843,159 +883,159 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="b">
+      <c r="B2" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="b">
+      <c r="B3" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="b">
+      <c r="B4" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="b">
+      <c r="B5" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="b">
+      <c r="B6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="b">
+      <c r="B7" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="b">
+      <c r="B8" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="b">
+      <c r="B9" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="b">
+      <c r="B10" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="b">
+      <c r="B11" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="b">
+      <c r="B12" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="b">
+      <c r="B13" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="b">
+      <c r="B14" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="b">
+      <c r="B15" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="b">
+      <c r="B16" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="b">
+      <c r="B17" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="b">
+      <c r="B18" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="b">
+      <c r="B19" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="b">
+      <c r="B20" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1003,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1011,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1019,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1027,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1035,7 +1075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1043,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1051,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1059,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -1067,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -1075,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1083,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -1091,7 +1131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1099,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1107,7 +1147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1115,7 +1155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -1123,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1131,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1139,7 +1179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -1147,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -1155,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1163,7 +1203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1171,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1179,7 +1219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1187,7 +1227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1195,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -1203,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -1211,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -1219,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1227,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1235,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -1243,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1251,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -1259,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -1267,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -1275,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -1283,7 +1323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -1291,7 +1331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -1299,7 +1339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -1307,7 +1347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -1315,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -1323,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -1331,7 +1371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -1339,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -1347,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -1355,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -1363,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -1371,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -1379,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -1387,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -1395,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -1403,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -1411,7 +1451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -1419,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -1427,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -1435,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -1443,7 +1483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -1459,7 +1499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -1467,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -1475,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -1483,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -1491,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -1499,7 +1539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -1507,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -1515,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -1523,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -1531,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -1539,7 +1579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -1547,7 +1587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -1555,7 +1595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -1563,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -1571,7 +1611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -1579,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -1587,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -1595,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -1603,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -1611,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -1619,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -1627,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -1635,7 +1675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -1643,7 +1683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -1651,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -1659,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -1667,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -1675,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -1683,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -1691,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -1699,7 +1739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -1707,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -1715,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -1723,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -1731,7 +1771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -1739,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -1747,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -1755,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -1763,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -1771,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -1779,7 +1819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -1787,7 +1827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -1795,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -1803,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -1811,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -1819,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -1827,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -1835,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -1843,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -1851,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -1861,16 +1901,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>129</v>
       </c>
@@ -1878,7 +1922,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>131</v>
       </c>
@@ -1886,7 +1930,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>133</v>
       </c>
@@ -1894,7 +1938,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -1902,7 +1946,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>137</v>
       </c>
@@ -1910,7 +1954,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>139</v>
       </c>
@@ -1918,7 +1962,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -1926,7 +1970,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>143</v>
       </c>
@@ -1934,7 +1978,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>145</v>
       </c>
@@ -1942,7 +1986,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -1952,16 +1996,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="39.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1969,7 +2017,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1977,7 +2025,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1985,7 +2033,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +2041,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2001,7 +2049,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2009,7 +2057,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -2017,7 +2065,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -2025,7 +2073,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -2033,7 +2081,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2041,7 +2089,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -2049,7 +2097,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2057,7 +2105,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2065,7 +2113,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -2073,7 +2121,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2081,7 +2129,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -2089,7 +2137,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2097,7 +2145,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2105,7 +2153,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -2113,7 +2161,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -2123,16 +2171,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="26.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>148</v>
       </c>
@@ -2146,154 +2200,154 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>149</v>
       </c>
       <c r="B2" t="s">
         <v>132</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>150</v>
       </c>
       <c r="B3" t="s">
         <v>134</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>151</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>152</v>
       </c>
       <c r="B5" t="s">
         <v>134</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>153</v>
       </c>
       <c r="B6" t="s">
         <v>145</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>153</v>
       </c>
       <c r="B7" t="s">
         <v>132</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>153</v>
       </c>
       <c r="B8" t="s">
         <v>134</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D8" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>153</v>
       </c>
       <c r="B9" t="s">
         <v>136</v>
       </c>
-      <c r="C9" t="s">
-        <v>163</v>
+      <c r="C9" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="D9" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>154</v>
       </c>
       <c r="B10" t="s">
         <v>134</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>155</v>
       </c>
       <c r="B11" t="s">
         <v>132</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>155</v>
       </c>
       <c r="B12" t="s">
         <v>134</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D12" t="s">
@@ -2302,6 +2356,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>